--- a/output/pdf_financials_xlsx/NSCI.xlsx
+++ b/output/pdf_financials_xlsx/NSCI.xlsx
@@ -3818,7 +3818,7 @@
         <v>-0.025275</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.074</v>
+        <v>-0.074</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-1.66</v>
@@ -3951,13 +3951,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.00725</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.002382</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>0.004868</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>0</v>
@@ -11512,7 +11512,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E109" s="5" t="n">
         <v>0.00725</v>
       </c>
@@ -11758,7 +11762,11 @@
           <t>Reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -12191,7 +12199,11 @@
           <t>Reserve (Note 4)</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -12263,7 +12275,7 @@
         </is>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0.074</v>
+        <v>-0.074</v>
       </c>
       <c r="G121" s="5" t="n">
         <v>-1.66</v>
@@ -20727,7 +20739,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr"/>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E262" s="5" t="n">
         <v>-0.00725</v>
       </c>

--- a/output/pdf_financials_xlsx/NSCI.xlsx
+++ b/output/pdf_financials_xlsx/NSCI.xlsx
@@ -721,13 +721,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.006123</v>
+        <v>0.025275</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.028168</v>
+        <v>0.173775</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.024616</v>
+        <v>0.098398</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.476</v>
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.006123</v>
+        <v>-0.025275</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>5.369832</v>
+        <v>5.224225</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>6.035384</v>
+        <v>5.961602</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-1.644</v>
@@ -792,10 +792,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001666</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005744</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>-0.328</v>
@@ -1376,10 +1376,10 @@
         <v>-0.025275</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.110109</v>
+        <v>-0.111775</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.168346</v>
+        <v>0.162602</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.35</v>
@@ -1444,10 +1444,10 @@
         <v>-0.025275</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.08489099999999999</v>
+        <v>0.08322499999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.500346</v>
+        <v>0.494602</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.284</v>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1.012898222169192</v>
+        <v>0.9930199260231476</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.982137733142038</v>
+        <v>5.913462458153993</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-29.00685801371602</v>
@@ -1588,7 +1588,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.071674</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.779</v>
@@ -1597,22 +1597,22 @@
         <v>6.619</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.158</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>10.405</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.525</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.759</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.376</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="35">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.071674</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.779</v>
@@ -1665,22 +1665,22 @@
         <v>6.619</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.158</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>10.405</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.525</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.759</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.376</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
     </row>
     <row r="37">
@@ -2073,22 +2073,22 @@
         <v>0.128</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.477</v>
+        <v>0.319</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>10.983</v>
+        <v>0.578</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>6.638</v>
+        <v>3.113</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.388</v>
+        <v>1.629</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.995</v>
+        <v>1.619</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>4.794</v>
+        <v>4.249</v>
       </c>
     </row>
     <row r="49">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
@@ -28724,17 +28724,17 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E395" s="5" t="n">
-        <v>-0.025275</v>
+        <v>0.025275</v>
       </c>
       <c r="F395" s="5" t="n">
-        <v>-0.173775</v>
+        <v>0.173775</v>
       </c>
       <c r="G395" s="5" t="n">
-        <v>-0.098398</v>
+        <v>0.098398</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">

--- a/output/pdf_financials_xlsx/NSCI.xlsx
+++ b/output/pdf_financials_xlsx/NSCI.xlsx
@@ -1410,28 +1410,28 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.195</v>
+        <v>0.372</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.332</v>
+        <v>0.845</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.066</v>
+        <v>1.77</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.816</v>
+        <v>2.567</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>2.967</v>
+        <v>4.649</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>3.003</v>
+        <v>4.666</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>3.105</v>
+        <v>4.626</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.223</v>
+        <v>3.427</v>
       </c>
     </row>
     <row r="29">
@@ -1444,28 +1444,28 @@
         <v>-0.025275</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.08322499999999999</v>
+        <v>0.260225</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.494602</v>
+        <v>1.007602</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.284</v>
+        <v>-1.58</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.046</v>
+        <v>0.797</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.698</v>
+        <v>-5.016</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-13.768</v>
+        <v>-12.105</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-10.463</v>
+        <v>-8.942</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.381</v>
+        <v>-2.177</v>
       </c>
     </row>
     <row r="30">
@@ -1480,28 +1480,28 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.9930199260231476</v>
+        <v>3.104939744660542</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.913462458153993</v>
+        <v>12.04689143950263</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-29.00685801371602</v>
+        <v>-20.06604013208026</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.2867294146979991</v>
+        <v>4.967898772050115</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-27.73384124880957</v>
+        <v>-20.76932632189143</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-346.7136741374969</v>
+        <v>-304.8350541425334</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-82.0884983524243</v>
+        <v>-70.15534285265966</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-33.93215576073866</v>
+        <v>-21.84865515857085</v>
       </c>
     </row>
     <row r="31">
@@ -3852,28 +3852,28 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.372</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.845</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>2.567</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>4.649</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>4.666</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>4.626</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>3.427</v>
       </c>
     </row>
     <row r="101">
@@ -4269,10 +4269,10 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -12370,7 +12370,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -12429,7 +12433,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -13092,7 +13096,11 @@
           <t>Additions to intangible assets 9</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -15372,7 +15380,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -15433,7 +15445,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -16100,7 +16112,11 @@
           <t>Additions to intangible assets 10</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -17243,7 +17259,11 @@
           <t>Depreciation of property and equipment 7</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -17302,7 +17322,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -17715,7 +17735,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -17768,7 +17792,11 @@
           <t>Proceeds on disposal of property and equipment 7</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -19021,7 +19049,11 @@
           <t>Proceeds on disposal of property plant and equipment</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -19511,7 +19543,11 @@
           <t>Depreciation of property and equipment 4,7</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/NSCI.xlsx
+++ b/output/pdf_financials_xlsx/NSCI.xlsx
@@ -934,7 +934,7 @@
         <v>0.168346</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-3.678</v>
+        <v>-3.975</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-1.772</v>
@@ -968,7 +968,7 @@
         <v>-0.261</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.297</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1382,7 +1382,7 @@
         <v>0.162602</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.35</v>
+        <v>-3.647</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.77</v>
@@ -1410,28 +1410,28 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.372</v>
+        <v>0.339</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.845</v>
+        <v>0.775</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.77</v>
+        <v>1.681</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2.567</v>
+        <v>2.505</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>4.649</v>
+        <v>4.564</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>4.666</v>
+        <v>4.365</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>4.626</v>
+        <v>4.353</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>3.427</v>
+        <v>3.188</v>
       </c>
     </row>
     <row r="29">
@@ -1444,28 +1444,28 @@
         <v>-0.025275</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.260225</v>
+        <v>0.227225</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.007602</v>
+        <v>0.937602</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.58</v>
+        <v>-1.966</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.797</v>
+        <v>0.735</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.016</v>
+        <v>-5.101</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-12.105</v>
+        <v>-12.406</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-8.942</v>
+        <v>-9.215</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.177</v>
+        <v>-2.416</v>
       </c>
     </row>
     <row r="30">
@@ -1480,28 +1480,28 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3.104939744660542</v>
+        <v>2.71119198186374</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>12.04689143950263</v>
+        <v>11.20997130559541</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-20.06604013208026</v>
+        <v>-24.96824993649987</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>4.967898772050115</v>
+        <v>4.581437387022377</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-20.76932632189143</v>
+        <v>-21.12127862200323</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-304.8350541425334</v>
+        <v>-312.4150088139008</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-70.15534285265966</v>
+        <v>-72.29719127569435</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-21.84865515857085</v>
+        <v>-24.24729024488157</v>
       </c>
     </row>
     <row r="31">
@@ -1520,7 +1520,7 @@
         <v>155.0378387368871</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-7.471698113207548</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5081,7 +5081,7 @@
         <v>-10.673</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-11.913</v>
+        <v>-11.92</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>3.207</v>
@@ -12492,7 +12492,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -13877,7 +13881,11 @@
           <t>Deferred tax recovery 21</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -14479,7 +14487,11 @@
           <t>Cash flows generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -15506,7 +15518,11 @@
           <t>Deferred tax recovery 16</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -17377,7 +17393,11 @@
           <t>Deferred tax recovery 13</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -19606,7 +19626,11 @@
           <t>Deferred tax expense 12</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -22292,7 +22316,11 @@
           <t>Depreciation and amortization expense 8,9</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -22758,7 +22786,11 @@
           <t>Deferred income tax (recovery) expense</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -23574,7 +23606,11 @@
           <t>Deferred income tax recovery 21</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E309" t="inlineStr">
         <is>
           <t>-</t>
@@ -24654,7 +24690,11 @@
           <t>Depreciation and amortization expense 9,10</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -25012,7 +25052,11 @@
           <t>Deferred income tax recovery 16</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -25976,7 +26020,11 @@
           <t>Depreciation and amortization expense 7,8</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -26271,7 +26319,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -27847,7 +27899,11 @@
           <t>Depreciation and amortization expense 4,7,8</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
